--- a/code/resultados/NWJSSP_OADG_EPR(VND).xlsx
+++ b/code/resultados/NWJSSP_OADG_EPR(VND).xlsx
@@ -12,6 +12,9 @@
     <sheet name="ft10" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,6 +622,228 @@
       <c r="B1" t="n">
         <v>246309</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>152</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D2" t="n">
+        <v>598</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>186</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I2" t="n">
+        <v>263</v>
+      </c>
+      <c r="J2" t="n">
+        <v>849</v>
+      </c>
+      <c r="K2" t="n">
+        <v>359</v>
+      </c>
+      <c r="L2" t="n">
+        <v>844</v>
+      </c>
+      <c r="M2" t="n">
+        <v>570</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="P2" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>490</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="S2" t="n">
+        <v>976</v>
+      </c>
+      <c r="T2" t="n">
+        <v>557</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>17290</v>
+      </c>
+      <c r="B1" t="n">
+        <v>284395</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1162</v>
+      </c>
+      <c r="C2" t="n">
+        <v>662</v>
+      </c>
+      <c r="D2" t="n">
+        <v>362</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>882</v>
+      </c>
+      <c r="G2" t="n">
+        <v>299</v>
+      </c>
+      <c r="H2" t="n">
+        <v>199</v>
+      </c>
+      <c r="I2" t="n">
+        <v>863</v>
+      </c>
+      <c r="J2" t="n">
+        <v>535</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81</v>
+      </c>
+      <c r="L2" t="n">
+        <v>94</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1345</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O2" t="n">
+        <v>830</v>
+      </c>
+      <c r="P2" t="n">
+        <v>533</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>406</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1476</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1031</v>
+      </c>
+      <c r="T2" t="n">
+        <v>263</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>94122</v>
+      </c>
+      <c r="B1" t="n">
+        <v>44909</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4829</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7278</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5204</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3140</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8786</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3829</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>94122</v>
+      </c>
+      <c r="B1" t="n">
+        <v>37016</v>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
@@ -627,77 +852,37 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr"/>
       <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>1050</v>
+        <v>4829</v>
       </c>
       <c r="D2" t="n">
-        <v>598</v>
+        <v>7278</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>5204</v>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>8183</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>3140</v>
       </c>
       <c r="H2" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>263</v>
+        <v>8786</v>
       </c>
       <c r="J2" t="n">
-        <v>849</v>
-      </c>
-      <c r="K2" t="n">
-        <v>359</v>
-      </c>
-      <c r="L2" t="n">
-        <v>844</v>
-      </c>
-      <c r="M2" t="n">
-        <v>570</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="P2" t="n">
-        <v>769</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>490</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1247</v>
-      </c>
-      <c r="S2" t="n">
-        <v>976</v>
-      </c>
-      <c r="T2" t="n">
-        <v>557</v>
+        <v>3829</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_EPR(VND).xlsx
+++ b/code/resultados/NWJSSP_OADG_EPR(VND).xlsx
@@ -15,6 +15,10 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +432,7 @@
         <v>308</v>
       </c>
       <c r="B1" t="n">
-        <v>2659</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="2">
@@ -449,6 +453,1076 @@
       </c>
       <c r="F2" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6587509</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600099</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>78980</v>
+      </c>
+      <c r="B2" t="n">
+        <v>27180</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100073</v>
+      </c>
+      <c r="D2" t="n">
+        <v>57826</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62780</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51045</v>
+      </c>
+      <c r="G2" t="n">
+        <v>131031</v>
+      </c>
+      <c r="H2" t="n">
+        <v>68028</v>
+      </c>
+      <c r="I2" t="n">
+        <v>33268</v>
+      </c>
+      <c r="J2" t="n">
+        <v>80379</v>
+      </c>
+      <c r="K2" t="n">
+        <v>34859</v>
+      </c>
+      <c r="L2" t="n">
+        <v>15552</v>
+      </c>
+      <c r="M2" t="n">
+        <v>112646</v>
+      </c>
+      <c r="N2" t="n">
+        <v>104916</v>
+      </c>
+      <c r="O2" t="n">
+        <v>66289</v>
+      </c>
+      <c r="P2" t="n">
+        <v>32272</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>41456</v>
+      </c>
+      <c r="R2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7553</v>
+      </c>
+      <c r="T2" t="n">
+        <v>23966</v>
+      </c>
+      <c r="U2" t="n">
+        <v>85748</v>
+      </c>
+      <c r="V2" t="n">
+        <v>69344</v>
+      </c>
+      <c r="W2" t="n">
+        <v>68840</v>
+      </c>
+      <c r="X2" t="n">
+        <v>126376</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>57886</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>84231</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4402</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>115934</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>103075</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1253</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>90440</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>99507</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>76847</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24962</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>54420</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>112372</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>133054</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>50191</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>80720</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>101649</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>125540</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>121114</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>43957</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>47545</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>89214</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11635</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>38519</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>70329</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>109312</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11029</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>95693</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>75446</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>22594</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>29687</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>39954</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>32148</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>91968</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>115554</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>42990</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>10037</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>40361</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>7203</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>116534</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>66523</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>95334</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>73274</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>6921</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>97356</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>19574</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>6426</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>13377</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>63207</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>12098</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>53340</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>51214</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>110033</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>92149</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>16907</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>97319</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>72686</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>20977</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>122747</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>3334</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>59606</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>120671</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>83441</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>81673</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>49340</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>53620</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>56690</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>30377</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>14959</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>22792</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>135773</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>28184</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>37339</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>107607</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44304018</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4029454</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>108959</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>160588</v>
+      </c>
+      <c r="D2" t="n">
+        <v>149358</v>
+      </c>
+      <c r="E2" t="n">
+        <v>197073</v>
+      </c>
+      <c r="F2" t="n">
+        <v>613914</v>
+      </c>
+      <c r="G2" t="n">
+        <v>343626</v>
+      </c>
+      <c r="H2" t="n">
+        <v>446263</v>
+      </c>
+      <c r="I2" t="n">
+        <v>440096</v>
+      </c>
+      <c r="J2" t="n">
+        <v>531583</v>
+      </c>
+      <c r="K2" t="n">
+        <v>36307</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5666</v>
+      </c>
+      <c r="M2" t="n">
+        <v>195705</v>
+      </c>
+      <c r="N2" t="n">
+        <v>480701</v>
+      </c>
+      <c r="O2" t="n">
+        <v>737218</v>
+      </c>
+      <c r="P2" t="n">
+        <v>803661</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>778132</v>
+      </c>
+      <c r="R2" t="n">
+        <v>249780</v>
+      </c>
+      <c r="S2" t="n">
+        <v>491644</v>
+      </c>
+      <c r="T2" t="n">
+        <v>328485</v>
+      </c>
+      <c r="U2" t="n">
+        <v>750378</v>
+      </c>
+      <c r="V2" t="n">
+        <v>376040</v>
+      </c>
+      <c r="W2" t="n">
+        <v>579795</v>
+      </c>
+      <c r="X2" t="n">
+        <v>352260</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>102743</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>93569</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>289121</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>767569</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>614198</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>633182</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>691035</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>604764</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>234392</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>92359</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>116342</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>462162</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>506843</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>596829</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>787965</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>355876</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>373148</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>498397</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>133964</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>114735</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8872</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>635089</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>828511</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>562395</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>535324</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>297881</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>760293</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>429408</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>839022</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>225480</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>206624</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>73099</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>19771</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>622200</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>56945</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>185853</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>262228</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>336248</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>705745</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>241461</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>728233</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>555290</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>142572</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>318426</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>648390</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>681501</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>679473</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>68170</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>198307</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>167517</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>313160</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>146034</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>168254</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>741099</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>304336</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>62923</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>511277</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>581998</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>457189</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>535118</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>389492</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>245198</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>412500</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>200800</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>703248</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>663365</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>403624</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>809368</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>50521</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>275678</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>412717</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>468571</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>13541</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>548546</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>6975</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>633065</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44746002</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4325441</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>180719</v>
+      </c>
+      <c r="B2" t="n">
+        <v>534880</v>
+      </c>
+      <c r="C2" t="n">
+        <v>367133</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34011</v>
+      </c>
+      <c r="E2" t="n">
+        <v>522806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>720745</v>
+      </c>
+      <c r="G2" t="n">
+        <v>632932</v>
+      </c>
+      <c r="H2" t="n">
+        <v>581</v>
+      </c>
+      <c r="I2" t="n">
+        <v>820049</v>
+      </c>
+      <c r="J2" t="n">
+        <v>151442</v>
+      </c>
+      <c r="K2" t="n">
+        <v>857513</v>
+      </c>
+      <c r="L2" t="n">
+        <v>494870</v>
+      </c>
+      <c r="M2" t="n">
+        <v>171360</v>
+      </c>
+      <c r="N2" t="n">
+        <v>675125</v>
+      </c>
+      <c r="O2" t="n">
+        <v>430788</v>
+      </c>
+      <c r="P2" t="n">
+        <v>575023</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>673979</v>
+      </c>
+      <c r="R2" t="n">
+        <v>250003</v>
+      </c>
+      <c r="S2" t="n">
+        <v>107630</v>
+      </c>
+      <c r="T2" t="n">
+        <v>340502</v>
+      </c>
+      <c r="U2" t="n">
+        <v>184189</v>
+      </c>
+      <c r="V2" t="n">
+        <v>160895</v>
+      </c>
+      <c r="W2" t="n">
+        <v>578200</v>
+      </c>
+      <c r="X2" t="n">
+        <v>470836</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>790288</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>459086</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>610581</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>582102</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>292219</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>476491</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>214355</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>264773</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>693821</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>193110</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>638589</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>122105</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>102070</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>26807</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>709112</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>645876</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>750902</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>100614</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>59686</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>208780</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>634984</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>310753</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>257698</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>338947</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>258054</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>72671</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>657927</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>515019</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>609467</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>357207</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>139455</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>730695</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>756207</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>768301</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>295409</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>83100</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>289687</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>516112</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>50548</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>792461</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>809328</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>61934</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>571019</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>732359</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>836240</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>516234</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>325609</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>443452</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>822975</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>391378</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>738149</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>87597</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>430466</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>20074</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>223266</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>371192</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>113494</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>220830</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>548820</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>490249</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>773142</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>232694</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>707</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>465142</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>232947</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>407792</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>291168</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>642928</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>379855</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>130694</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>134663</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>70827</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>412660</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>182669</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>322501</v>
       </c>
     </row>
   </sheetData>
@@ -470,7 +1544,7 @@
         <v>321</v>
       </c>
       <c r="B1" t="n">
-        <v>2181</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="2">
@@ -509,42 +1583,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9814</v>
+        <v>9808</v>
       </c>
       <c r="B1" t="n">
-        <v>29119</v>
+        <v>19826</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>486</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>925</v>
+        <v>1135</v>
       </c>
       <c r="D2" t="n">
-        <v>725</v>
+        <v>979</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>366</v>
+        <v>755</v>
       </c>
       <c r="G2" t="n">
-        <v>209</v>
+        <v>552</v>
       </c>
       <c r="H2" t="n">
-        <v>562</v>
+        <v>604</v>
       </c>
       <c r="I2" t="n">
-        <v>1170</v>
+        <v>84</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -563,42 +1637,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>10077</v>
+        <v>10212</v>
       </c>
       <c r="B1" t="n">
-        <v>30039</v>
+        <v>10108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="D2" t="n">
-        <v>929</v>
+        <v>669</v>
       </c>
       <c r="E2" t="n">
-        <v>560</v>
+        <v>616</v>
       </c>
       <c r="F2" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G2" t="n">
         <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>766</v>
+        <v>375</v>
       </c>
       <c r="I2" t="n">
-        <v>627</v>
+        <v>769</v>
       </c>
       <c r="J2" t="n">
-        <v>495</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -617,72 +1691,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>16804</v>
+        <v>17100</v>
       </c>
       <c r="B1" t="n">
-        <v>246309</v>
+        <v>330064</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>514</v>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
+        <v>1237</v>
       </c>
       <c r="C2" t="n">
-        <v>1050</v>
+        <v>1078</v>
       </c>
       <c r="D2" t="n">
-        <v>598</v>
+        <v>752</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>392</v>
       </c>
       <c r="H2" t="n">
-        <v>118</v>
+        <v>466</v>
       </c>
       <c r="I2" t="n">
-        <v>263</v>
+        <v>1348</v>
       </c>
       <c r="J2" t="n">
-        <v>849</v>
+        <v>913</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>178</v>
       </c>
       <c r="L2" t="n">
-        <v>844</v>
+        <v>184</v>
       </c>
       <c r="M2" t="n">
-        <v>570</v>
+        <v>740</v>
       </c>
       <c r="N2" t="n">
-        <v>1400</v>
+        <v>1329</v>
       </c>
       <c r="O2" t="n">
-        <v>1215</v>
+        <v>640</v>
       </c>
       <c r="P2" t="n">
-        <v>769</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="n">
-        <v>490</v>
+        <v>303</v>
       </c>
       <c r="R2" t="n">
-        <v>1247</v>
+        <v>912</v>
       </c>
       <c r="S2" t="n">
-        <v>976</v>
+        <v>556</v>
       </c>
       <c r="T2" t="n">
-        <v>557</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -701,72 +1775,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>17290</v>
+        <v>17260</v>
       </c>
       <c r="B1" t="n">
-        <v>284395</v>
+        <v>336185</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="B2" t="n">
-        <v>1162</v>
+        <v>598</v>
       </c>
       <c r="C2" t="n">
-        <v>662</v>
+        <v>816</v>
       </c>
       <c r="D2" t="n">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>882</v>
+        <v>635</v>
       </c>
       <c r="G2" t="n">
-        <v>299</v>
+        <v>449</v>
       </c>
       <c r="H2" t="n">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="I2" t="n">
-        <v>863</v>
+        <v>709</v>
       </c>
       <c r="J2" t="n">
-        <v>535</v>
+        <v>1495</v>
       </c>
       <c r="K2" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="M2" t="n">
-        <v>1345</v>
+        <v>280</v>
       </c>
       <c r="N2" t="n">
-        <v>1151</v>
+        <v>1249</v>
       </c>
       <c r="O2" t="n">
-        <v>830</v>
+        <v>1049</v>
       </c>
       <c r="P2" t="n">
-        <v>533</v>
+        <v>1204</v>
       </c>
       <c r="Q2" t="n">
-        <v>406</v>
+        <v>556</v>
       </c>
       <c r="R2" t="n">
-        <v>1476</v>
+        <v>1120</v>
       </c>
       <c r="S2" t="n">
-        <v>1031</v>
+        <v>986</v>
       </c>
       <c r="T2" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +1862,7 @@
         <v>94122</v>
       </c>
       <c r="B1" t="n">
-        <v>44909</v>
+        <v>29152</v>
       </c>
     </row>
     <row r="2">
@@ -839,50 +1913,366 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>94122</v>
+        <v>98721</v>
       </c>
       <c r="B1" t="n">
-        <v>37016</v>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
+        <v>26720</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>1033</v>
       </c>
       <c r="C2" t="n">
-        <v>4829</v>
+        <v>6539</v>
       </c>
       <c r="D2" t="n">
-        <v>7278</v>
+        <v>8547</v>
       </c>
       <c r="E2" t="n">
-        <v>5204</v>
+        <v>6914</v>
       </c>
       <c r="F2" t="n">
-        <v>8183</v>
+        <v>9691</v>
       </c>
       <c r="G2" t="n">
-        <v>3140</v>
+        <v>4850</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>8786</v>
+        <v>2070</v>
       </c>
       <c r="J2" t="n">
-        <v>3829</v>
+        <v>5521</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6537532</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3600009</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>32329</v>
+      </c>
+      <c r="B2" t="n">
+        <v>99535</v>
+      </c>
+      <c r="C2" t="n">
+        <v>99360</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22866</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2229</v>
+      </c>
+      <c r="F2" t="n">
+        <v>73526</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44919</v>
+      </c>
+      <c r="H2" t="n">
+        <v>104218</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26525</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40549</v>
+      </c>
+      <c r="K2" t="n">
+        <v>113380</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2602</v>
+      </c>
+      <c r="M2" t="n">
+        <v>131089</v>
+      </c>
+      <c r="N2" t="n">
+        <v>122710</v>
+      </c>
+      <c r="O2" t="n">
+        <v>191</v>
+      </c>
+      <c r="P2" t="n">
+        <v>491</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7989</v>
+      </c>
+      <c r="R2" t="n">
+        <v>42364</v>
+      </c>
+      <c r="S2" t="n">
+        <v>41344</v>
+      </c>
+      <c r="T2" t="n">
+        <v>67192</v>
+      </c>
+      <c r="U2" t="n">
+        <v>86249</v>
+      </c>
+      <c r="V2" t="n">
+        <v>73276</v>
+      </c>
+      <c r="W2" t="n">
+        <v>23875</v>
+      </c>
+      <c r="X2" t="n">
+        <v>13907</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5518</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>108930</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>79738</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>53155</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>20345</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15545</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6004</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>113340</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>78522</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>50096</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>80908</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21930</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>71711</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>92944</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>9795</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>121845</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18938</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>130916</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>68599</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>35227</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>60291</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>26525</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>120978</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>125444</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>62761</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>114280</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>78638</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>93289</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>62213</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>94949</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11495</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4152</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>31183</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8933</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>117349</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>74166</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>89040</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>17396</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>86532</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>16408</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>34435</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>88225</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>83743</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>7977</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>84498</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>90541</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>95785</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>38405</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>28047</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>111774</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>91976</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>58922</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>103063</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>54577</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>118676</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>59661</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>108997</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>49244</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>18313</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>67872</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>64842</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>31740</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>52461</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>106582</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>37510</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>50072</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>29139</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>11722</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>57353</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>47570</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>42577</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>77516</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>103160</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>127793</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_EPR(VND).xlsx
+++ b/code/resultados/NWJSSP_OADG_EPR(VND).xlsx
@@ -19,6 +19,8 @@
     <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +434,7 @@
         <v>308</v>
       </c>
       <c r="B1" t="n">
-        <v>1301</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2">
@@ -471,312 +473,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6587509</v>
+        <v>6402336</v>
       </c>
       <c r="B1" t="n">
-        <v>3600099</v>
+        <v>3611184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78980</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27180</v>
+        <v>78202</v>
       </c>
       <c r="C2" t="n">
-        <v>100073</v>
+        <v>89927</v>
       </c>
       <c r="D2" t="n">
-        <v>57826</v>
+        <v>27680</v>
       </c>
       <c r="E2" t="n">
-        <v>62780</v>
+        <v>6231</v>
       </c>
       <c r="F2" t="n">
-        <v>51045</v>
+        <v>64507</v>
       </c>
       <c r="G2" t="n">
-        <v>131031</v>
+        <v>76206</v>
       </c>
       <c r="H2" t="n">
-        <v>68028</v>
+        <v>20880</v>
       </c>
       <c r="I2" t="n">
-        <v>33268</v>
+        <v>98435</v>
       </c>
       <c r="J2" t="n">
-        <v>80379</v>
+        <v>52772</v>
       </c>
       <c r="K2" t="n">
-        <v>34859</v>
+        <v>126078</v>
       </c>
       <c r="L2" t="n">
-        <v>15552</v>
+        <v>121005</v>
       </c>
       <c r="M2" t="n">
-        <v>112646</v>
+        <v>96311</v>
       </c>
       <c r="N2" t="n">
-        <v>104916</v>
+        <v>15111</v>
       </c>
       <c r="O2" t="n">
-        <v>66289</v>
+        <v>80128</v>
       </c>
       <c r="P2" t="n">
-        <v>32272</v>
+        <v>112094</v>
       </c>
       <c r="Q2" t="n">
-        <v>41456</v>
+        <v>28904</v>
       </c>
       <c r="R2" t="n">
-        <v>46102</v>
+        <v>100497</v>
       </c>
       <c r="S2" t="n">
-        <v>7553</v>
+        <v>114476</v>
       </c>
       <c r="T2" t="n">
-        <v>23966</v>
+        <v>94502</v>
       </c>
       <c r="U2" t="n">
-        <v>85748</v>
+        <v>101238</v>
       </c>
       <c r="V2" t="n">
-        <v>69344</v>
+        <v>1064</v>
       </c>
       <c r="W2" t="n">
-        <v>68840</v>
+        <v>52767</v>
       </c>
       <c r="X2" t="n">
-        <v>126376</v>
+        <v>104476</v>
       </c>
       <c r="Y2" t="n">
-        <v>57886</v>
+        <v>107777</v>
       </c>
       <c r="Z2" t="n">
-        <v>84231</v>
+        <v>39405</v>
       </c>
       <c r="AA2" t="n">
-        <v>4402</v>
+        <v>39018</v>
       </c>
       <c r="AB2" t="n">
-        <v>115934</v>
+        <v>129228</v>
       </c>
       <c r="AC2" t="n">
-        <v>103075</v>
+        <v>67751</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>126512</v>
       </c>
       <c r="AE2" t="n">
-        <v>1253</v>
+        <v>71461</v>
       </c>
       <c r="AF2" t="n">
-        <v>90440</v>
+        <v>67646</v>
       </c>
       <c r="AG2" t="n">
-        <v>99507</v>
+        <v>82999</v>
       </c>
       <c r="AH2" t="n">
-        <v>76847</v>
+        <v>122107</v>
       </c>
       <c r="AI2" t="n">
-        <v>24962</v>
+        <v>48517</v>
       </c>
       <c r="AJ2" t="n">
-        <v>54420</v>
+        <v>20325</v>
       </c>
       <c r="AK2" t="n">
-        <v>112372</v>
+        <v>54712</v>
       </c>
       <c r="AL2" t="n">
-        <v>133054</v>
+        <v>78950</v>
       </c>
       <c r="AM2" t="n">
-        <v>50191</v>
+        <v>119801</v>
       </c>
       <c r="AN2" t="n">
-        <v>80720</v>
+        <v>111246</v>
       </c>
       <c r="AO2" t="n">
-        <v>101649</v>
+        <v>49221</v>
       </c>
       <c r="AP2" t="n">
-        <v>125540</v>
+        <v>84242</v>
       </c>
       <c r="AQ2" t="n">
-        <v>121114</v>
+        <v>56312</v>
       </c>
       <c r="AR2" t="n">
-        <v>43957</v>
+        <v>26453</v>
       </c>
       <c r="AS2" t="n">
-        <v>47545</v>
+        <v>1180</v>
       </c>
       <c r="AT2" t="n">
-        <v>89214</v>
+        <v>11310</v>
       </c>
       <c r="AU2" t="n">
-        <v>11635</v>
+        <v>116692</v>
       </c>
       <c r="AV2" t="n">
-        <v>38519</v>
+        <v>46942</v>
       </c>
       <c r="AW2" t="n">
-        <v>70329</v>
+        <v>85158</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>5922</v>
       </c>
       <c r="AY2" t="n">
-        <v>109312</v>
+        <v>44227</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11029</v>
+        <v>94180</v>
       </c>
       <c r="BA2" t="n">
-        <v>95693</v>
+        <v>18664</v>
       </c>
       <c r="BB2" t="n">
-        <v>75446</v>
+        <v>60116</v>
       </c>
       <c r="BC2" t="n">
-        <v>22594</v>
+        <v>87073</v>
       </c>
       <c r="BD2" t="n">
-        <v>29687</v>
+        <v>61611</v>
       </c>
       <c r="BE2" t="n">
-        <v>39954</v>
+        <v>33680</v>
       </c>
       <c r="BF2" t="n">
-        <v>32148</v>
+        <v>15521</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>45221</v>
       </c>
       <c r="BH2" t="n">
-        <v>91968</v>
+        <v>38953</v>
       </c>
       <c r="BI2" t="n">
-        <v>115554</v>
+        <v>7476</v>
       </c>
       <c r="BJ2" t="n">
-        <v>42990</v>
+        <v>45735</v>
       </c>
       <c r="BK2" t="n">
-        <v>10037</v>
+        <v>17430</v>
       </c>
       <c r="BL2" t="n">
-        <v>40361</v>
+        <v>33579</v>
       </c>
       <c r="BM2" t="n">
-        <v>7203</v>
+        <v>102884</v>
       </c>
       <c r="BN2" t="n">
-        <v>116534</v>
+        <v>73814</v>
       </c>
       <c r="BO2" t="n">
-        <v>66523</v>
+        <v>15183</v>
       </c>
       <c r="BP2" t="n">
-        <v>95334</v>
+        <v>64021</v>
       </c>
       <c r="BQ2" t="n">
-        <v>73274</v>
+        <v>74079</v>
       </c>
       <c r="BR2" t="n">
-        <v>6921</v>
+        <v>25904</v>
       </c>
       <c r="BS2" t="n">
-        <v>97356</v>
+        <v>56254</v>
       </c>
       <c r="BT2" t="n">
-        <v>19574</v>
+        <v>35313</v>
       </c>
       <c r="BU2" t="n">
-        <v>6426</v>
+        <v>13167</v>
       </c>
       <c r="BV2" t="n">
-        <v>13377</v>
+        <v>20650</v>
       </c>
       <c r="BW2" t="n">
-        <v>63207</v>
+        <v>34220</v>
       </c>
       <c r="BX2" t="n">
-        <v>12098</v>
+        <v>9917</v>
       </c>
       <c r="BY2" t="n">
-        <v>53340</v>
+        <v>71346</v>
       </c>
       <c r="BZ2" t="n">
-        <v>51214</v>
+        <v>68199</v>
       </c>
       <c r="CA2" t="n">
-        <v>110033</v>
+        <v>38744</v>
       </c>
       <c r="CB2" t="n">
-        <v>92149</v>
+        <v>132632</v>
       </c>
       <c r="CC2" t="n">
-        <v>16907</v>
+        <v>57752</v>
       </c>
       <c r="CD2" t="n">
-        <v>97319</v>
+        <v>120943</v>
       </c>
       <c r="CE2" t="n">
-        <v>72686</v>
+        <v>4453</v>
       </c>
       <c r="CF2" t="n">
-        <v>20977</v>
+        <v>61928</v>
       </c>
       <c r="CG2" t="n">
-        <v>122747</v>
+        <v>39190</v>
       </c>
       <c r="CH2" t="n">
-        <v>3334</v>
+        <v>71426</v>
       </c>
       <c r="CI2" t="n">
-        <v>59606</v>
+        <v>88872</v>
       </c>
       <c r="CJ2" t="n">
-        <v>120671</v>
+        <v>23052</v>
       </c>
       <c r="CK2" t="n">
-        <v>83441</v>
+        <v>91287</v>
       </c>
       <c r="CL2" t="n">
-        <v>81673</v>
+        <v>107319</v>
       </c>
       <c r="CM2" t="n">
-        <v>49340</v>
+        <v>12319</v>
       </c>
       <c r="CN2" t="n">
-        <v>53620</v>
+        <v>106</v>
       </c>
       <c r="CO2" t="n">
-        <v>56690</v>
+        <v>28007</v>
       </c>
       <c r="CP2" t="n">
-        <v>30377</v>
+        <v>23948</v>
       </c>
       <c r="CQ2" t="n">
-        <v>14959</v>
+        <v>96385</v>
       </c>
       <c r="CR2" t="n">
-        <v>22792</v>
+        <v>8343</v>
       </c>
       <c r="CS2" t="n">
-        <v>135773</v>
+        <v>51668</v>
       </c>
       <c r="CT2" t="n">
-        <v>28184</v>
+        <v>2942</v>
       </c>
       <c r="CU2" t="n">
-        <v>37339</v>
+        <v>30560</v>
       </c>
       <c r="CV2" t="n">
-        <v>107607</v>
+        <v>102839</v>
       </c>
     </row>
   </sheetData>
@@ -795,312 +797,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>44304018</v>
+        <v>44322949</v>
       </c>
       <c r="B1" t="n">
-        <v>4029454</v>
+        <v>4373288</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108959</v>
+        <v>299257</v>
       </c>
       <c r="B2" t="n">
+        <v>534756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>445572</v>
+      </c>
+      <c r="D2" t="n">
+        <v>254470</v>
+      </c>
+      <c r="E2" t="n">
+        <v>342190</v>
+      </c>
+      <c r="F2" t="n">
+        <v>74155</v>
+      </c>
+      <c r="G2" t="n">
+        <v>64880</v>
+      </c>
+      <c r="H2" t="n">
+        <v>552873</v>
+      </c>
+      <c r="I2" t="n">
+        <v>668670</v>
+      </c>
+      <c r="J2" t="n">
+        <v>645279</v>
+      </c>
+      <c r="K2" t="n">
+        <v>375551</v>
+      </c>
+      <c r="L2" t="n">
+        <v>770565</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9774</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3862</v>
+      </c>
+      <c r="O2" t="n">
+        <v>457160</v>
+      </c>
+      <c r="P2" t="n">
+        <v>401752</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>21295</v>
+      </c>
+      <c r="R2" t="n">
+        <v>129039</v>
+      </c>
+      <c r="S2" t="n">
+        <v>426277</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>160588</v>
-      </c>
-      <c r="D2" t="n">
-        <v>149358</v>
-      </c>
-      <c r="E2" t="n">
-        <v>197073</v>
-      </c>
-      <c r="F2" t="n">
-        <v>613914</v>
-      </c>
-      <c r="G2" t="n">
-        <v>343626</v>
-      </c>
-      <c r="H2" t="n">
-        <v>446263</v>
-      </c>
-      <c r="I2" t="n">
-        <v>440096</v>
-      </c>
-      <c r="J2" t="n">
-        <v>531583</v>
-      </c>
-      <c r="K2" t="n">
-        <v>36307</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5666</v>
-      </c>
-      <c r="M2" t="n">
-        <v>195705</v>
-      </c>
-      <c r="N2" t="n">
-        <v>480701</v>
-      </c>
-      <c r="O2" t="n">
-        <v>737218</v>
-      </c>
-      <c r="P2" t="n">
-        <v>803661</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>778132</v>
-      </c>
-      <c r="R2" t="n">
-        <v>249780</v>
-      </c>
-      <c r="S2" t="n">
-        <v>491644</v>
-      </c>
-      <c r="T2" t="n">
-        <v>328485</v>
-      </c>
       <c r="U2" t="n">
-        <v>750378</v>
+        <v>588829</v>
       </c>
       <c r="V2" t="n">
-        <v>376040</v>
+        <v>498335</v>
       </c>
       <c r="W2" t="n">
-        <v>579795</v>
+        <v>58503</v>
       </c>
       <c r="X2" t="n">
-        <v>352260</v>
+        <v>623953</v>
       </c>
       <c r="Y2" t="n">
-        <v>102743</v>
+        <v>138504</v>
       </c>
       <c r="Z2" t="n">
-        <v>93569</v>
+        <v>602116</v>
       </c>
       <c r="AA2" t="n">
-        <v>289121</v>
+        <v>120917</v>
       </c>
       <c r="AB2" t="n">
-        <v>767569</v>
+        <v>35514</v>
       </c>
       <c r="AC2" t="n">
-        <v>614198</v>
+        <v>572652</v>
       </c>
       <c r="AD2" t="n">
-        <v>633182</v>
+        <v>56595</v>
       </c>
       <c r="AE2" t="n">
-        <v>691035</v>
+        <v>339228</v>
       </c>
       <c r="AF2" t="n">
-        <v>604764</v>
+        <v>207433</v>
       </c>
       <c r="AG2" t="n">
-        <v>234392</v>
+        <v>461279</v>
       </c>
       <c r="AH2" t="n">
-        <v>92359</v>
+        <v>230824</v>
       </c>
       <c r="AI2" t="n">
-        <v>116342</v>
+        <v>191546</v>
       </c>
       <c r="AJ2" t="n">
-        <v>462162</v>
+        <v>330749</v>
       </c>
       <c r="AK2" t="n">
-        <v>506843</v>
+        <v>265945</v>
       </c>
       <c r="AL2" t="n">
-        <v>596829</v>
+        <v>476655</v>
       </c>
       <c r="AM2" t="n">
-        <v>787965</v>
+        <v>742512</v>
       </c>
       <c r="AN2" t="n">
-        <v>355876</v>
+        <v>176561</v>
       </c>
       <c r="AO2" t="n">
-        <v>373148</v>
+        <v>354629</v>
       </c>
       <c r="AP2" t="n">
-        <v>498397</v>
+        <v>264228</v>
       </c>
       <c r="AQ2" t="n">
-        <v>133964</v>
+        <v>793</v>
       </c>
       <c r="AR2" t="n">
-        <v>114735</v>
+        <v>391319</v>
       </c>
       <c r="AS2" t="n">
-        <v>8872</v>
+        <v>543749</v>
       </c>
       <c r="AT2" t="n">
-        <v>635089</v>
+        <v>294448</v>
       </c>
       <c r="AU2" t="n">
-        <v>828511</v>
+        <v>549956</v>
       </c>
       <c r="AV2" t="n">
-        <v>562395</v>
+        <v>615655</v>
       </c>
       <c r="AW2" t="n">
-        <v>535324</v>
+        <v>510713</v>
       </c>
       <c r="AX2" t="n">
-        <v>297881</v>
+        <v>493914</v>
       </c>
       <c r="AY2" t="n">
-        <v>760293</v>
+        <v>708343</v>
       </c>
       <c r="AZ2" t="n">
-        <v>429408</v>
+        <v>748600</v>
       </c>
       <c r="BA2" t="n">
-        <v>839022</v>
+        <v>325223</v>
       </c>
       <c r="BB2" t="n">
-        <v>225480</v>
+        <v>400943</v>
       </c>
       <c r="BC2" t="n">
-        <v>206624</v>
+        <v>403276</v>
       </c>
       <c r="BD2" t="n">
-        <v>73099</v>
+        <v>108278</v>
       </c>
       <c r="BE2" t="n">
-        <v>19771</v>
+        <v>381085</v>
       </c>
       <c r="BF2" t="n">
-        <v>622200</v>
+        <v>709418</v>
       </c>
       <c r="BG2" t="n">
-        <v>56945</v>
+        <v>196473</v>
       </c>
       <c r="BH2" t="n">
-        <v>185853</v>
+        <v>819771</v>
       </c>
       <c r="BI2" t="n">
-        <v>262228</v>
+        <v>753410</v>
       </c>
       <c r="BJ2" t="n">
-        <v>336248</v>
+        <v>765409</v>
       </c>
       <c r="BK2" t="n">
-        <v>705745</v>
+        <v>149651</v>
       </c>
       <c r="BL2" t="n">
-        <v>241461</v>
+        <v>614124</v>
       </c>
       <c r="BM2" t="n">
-        <v>728233</v>
+        <v>795409</v>
       </c>
       <c r="BN2" t="n">
-        <v>555290</v>
+        <v>683231</v>
       </c>
       <c r="BO2" t="n">
-        <v>142572</v>
+        <v>587450</v>
       </c>
       <c r="BP2" t="n">
-        <v>318426</v>
+        <v>349525</v>
       </c>
       <c r="BQ2" t="n">
-        <v>648390</v>
+        <v>644553</v>
       </c>
       <c r="BR2" t="n">
-        <v>681501</v>
+        <v>434147</v>
       </c>
       <c r="BS2" t="n">
-        <v>679473</v>
+        <v>527711</v>
       </c>
       <c r="BT2" t="n">
-        <v>68170</v>
+        <v>804894</v>
       </c>
       <c r="BU2" t="n">
-        <v>198307</v>
+        <v>88328</v>
       </c>
       <c r="BV2" t="n">
-        <v>167517</v>
+        <v>786637</v>
       </c>
       <c r="BW2" t="n">
-        <v>313160</v>
+        <v>475185</v>
       </c>
       <c r="BX2" t="n">
-        <v>146034</v>
+        <v>598017</v>
       </c>
       <c r="BY2" t="n">
-        <v>168254</v>
+        <v>304970</v>
       </c>
       <c r="BZ2" t="n">
-        <v>741099</v>
+        <v>292518</v>
       </c>
       <c r="CA2" t="n">
-        <v>304336</v>
+        <v>177647</v>
       </c>
       <c r="CB2" t="n">
-        <v>62923</v>
+        <v>544843</v>
       </c>
       <c r="CC2" t="n">
-        <v>511277</v>
+        <v>270371</v>
       </c>
       <c r="CD2" t="n">
-        <v>581998</v>
+        <v>106681</v>
       </c>
       <c r="CE2" t="n">
-        <v>457189</v>
+        <v>210555</v>
       </c>
       <c r="CF2" t="n">
-        <v>535118</v>
+        <v>460140</v>
       </c>
       <c r="CG2" t="n">
-        <v>389492</v>
+        <v>222042</v>
       </c>
       <c r="CH2" t="n">
-        <v>245198</v>
+        <v>693202</v>
       </c>
       <c r="CI2" t="n">
-        <v>412500</v>
+        <v>142157</v>
       </c>
       <c r="CJ2" t="n">
-        <v>200800</v>
+        <v>313564</v>
       </c>
       <c r="CK2" t="n">
-        <v>703248</v>
+        <v>105128</v>
       </c>
       <c r="CL2" t="n">
-        <v>663365</v>
+        <v>674099</v>
       </c>
       <c r="CM2" t="n">
-        <v>403624</v>
+        <v>653153</v>
       </c>
       <c r="CN2" t="n">
-        <v>809368</v>
+        <v>243357</v>
       </c>
       <c r="CO2" t="n">
-        <v>50521</v>
+        <v>200006</v>
       </c>
       <c r="CP2" t="n">
-        <v>275678</v>
+        <v>160366</v>
       </c>
       <c r="CQ2" t="n">
-        <v>412717</v>
+        <v>721577</v>
       </c>
       <c r="CR2" t="n">
-        <v>468571</v>
+        <v>811538</v>
       </c>
       <c r="CS2" t="n">
-        <v>13541</v>
+        <v>697098</v>
       </c>
       <c r="CT2" t="n">
-        <v>548546</v>
+        <v>8445</v>
       </c>
       <c r="CU2" t="n">
-        <v>6975</v>
+        <v>85744</v>
       </c>
       <c r="CV2" t="n">
-        <v>633065</v>
+        <v>150558</v>
       </c>
     </row>
   </sheetData>
@@ -1119,10 +1121,3358 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>44746002</v>
+        <v>44521738</v>
       </c>
       <c r="B1" t="n">
-        <v>4325441</v>
+        <v>3897177</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>670934</v>
+      </c>
+      <c r="B2" t="n">
+        <v>42494</v>
+      </c>
+      <c r="C2" t="n">
+        <v>130752</v>
+      </c>
+      <c r="D2" t="n">
+        <v>744960</v>
+      </c>
+      <c r="E2" t="n">
+        <v>700168</v>
+      </c>
+      <c r="F2" t="n">
+        <v>238781</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17751</v>
+      </c>
+      <c r="H2" t="n">
+        <v>529422</v>
+      </c>
+      <c r="I2" t="n">
+        <v>405133</v>
+      </c>
+      <c r="J2" t="n">
+        <v>492913</v>
+      </c>
+      <c r="K2" t="n">
+        <v>476433</v>
+      </c>
+      <c r="L2" t="n">
+        <v>529786</v>
+      </c>
+      <c r="M2" t="n">
+        <v>730550</v>
+      </c>
+      <c r="N2" t="n">
+        <v>587927</v>
+      </c>
+      <c r="O2" t="n">
+        <v>253872</v>
+      </c>
+      <c r="P2" t="n">
+        <v>106948</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>628434</v>
+      </c>
+      <c r="R2" t="n">
+        <v>140469</v>
+      </c>
+      <c r="S2" t="n">
+        <v>420033</v>
+      </c>
+      <c r="T2" t="n">
+        <v>343449</v>
+      </c>
+      <c r="U2" t="n">
+        <v>277052</v>
+      </c>
+      <c r="V2" t="n">
+        <v>699790</v>
+      </c>
+      <c r="W2" t="n">
+        <v>52190</v>
+      </c>
+      <c r="X2" t="n">
+        <v>173529</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>715952</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>192792</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>217892</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>496919</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>754201</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>780548</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>426596</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>204828</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>394363</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>637799</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>225269</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>62072</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>567136</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>461870</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>72704</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>340708</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>94842</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>317463</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>162712</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>165541</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>676654</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>77804</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>719791</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>614420</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>202623</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>829873</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>367530</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>290772</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>599892</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>134801</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>543622</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>770415</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2985</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>804429</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>200004</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>194653</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>448577</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>365148</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>27374</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>834112</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>264422</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>109657</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>348604</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>500060</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>833403</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>652551</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>544388</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>309215</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>455747</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>256626</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>145089</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>384806</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>327153</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>366655</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>91521</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>427875</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>904</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>510497</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>798866</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>623243</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>121887</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>229190</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>296865</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>716070</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>561496</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>476390</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>73957</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>13417</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>37</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>672961</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>440636</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>580243</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>617637</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>783636</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>595910</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>580822638</v>
+      </c>
+      <c r="B1" t="n">
+        <v>6027127</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>434657</v>
+      </c>
+      <c r="B2" t="n">
+        <v>737746</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1048019</v>
+      </c>
+      <c r="D2" t="n">
+        <v>461341</v>
+      </c>
+      <c r="E2" t="n">
+        <v>132161</v>
+      </c>
+      <c r="F2" t="n">
+        <v>907542</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1055605</v>
+      </c>
+      <c r="H2" t="n">
+        <v>64615</v>
+      </c>
+      <c r="I2" t="n">
+        <v>87722</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1085553</v>
+      </c>
+      <c r="K2" t="n">
+        <v>635888</v>
+      </c>
+      <c r="L2" t="n">
+        <v>592284</v>
+      </c>
+      <c r="M2" t="n">
+        <v>355594</v>
+      </c>
+      <c r="N2" t="n">
+        <v>448594</v>
+      </c>
+      <c r="O2" t="n">
+        <v>751362</v>
+      </c>
+      <c r="P2" t="n">
+        <v>682050</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>514080</v>
+      </c>
+      <c r="R2" t="n">
+        <v>288923</v>
+      </c>
+      <c r="S2" t="n">
+        <v>663428</v>
+      </c>
+      <c r="T2" t="n">
+        <v>568628</v>
+      </c>
+      <c r="U2" t="n">
+        <v>581669</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1149821</v>
+      </c>
+      <c r="W2" t="n">
+        <v>630267</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1201399</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1051171</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>201408</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>184826</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>905405</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>154311</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>159746</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>573440</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>148935</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>188511</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>627222</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>942962</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>840775</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>478514</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1114649</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>665867</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>249339</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>170469</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>716900</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>61269</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>80996</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>481242</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>90003</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>399548</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>645935</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1007016</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>195602</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>759152</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>21777</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1115465</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>362620</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>290038</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1029556</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>649497</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>175949</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>453223</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1052852</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>147149</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>638857</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>705355</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1087379</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>991130</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>602947</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>916213</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>531188</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>961230</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>669212</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>454905</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>583372</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>479868</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1013120</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>259573</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1017539</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>658504</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>548821</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>306576</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>508653</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>675068</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1182105</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1113227</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>933922</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>827907</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1091562</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>901731</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>730567</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1021517</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>850532</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>718089</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>182363</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>719645</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>179078</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>794722</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>737961</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>41241</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>724854</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>152978</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>620345</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>481455</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>16382</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1148116</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>234702</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>24246</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1004933</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>333939</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>897402</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1103385</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>585901</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1030975</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>778959</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>338447</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>66866</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1035232</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>44930</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>577242</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>555669</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1080269</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>418696</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>350652</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>163493</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>142944</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>202013</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>71736</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>352057</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>135700</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>402473</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>543029</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>217249</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>789775</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>428538</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>13833</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>76681</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>496279</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>422338</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>363515</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>369872</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>395499</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1053402</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>122357</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>268349</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>458628</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>752493</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>623950</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>566913</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>512009</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>165238</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>84345</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>618629</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>534442</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>643661</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>261327</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>308695</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1105976</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>359496</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1193634</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>861310</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>335425</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>713309</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>982524</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>394804</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>539575</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>129444</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>817921</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>274349</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>963074</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>482037</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>1210991</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>468541</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>698583</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>565159</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>930643</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>600470</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>1021</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>562334</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>1025033</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>353155</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>1170683</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>638723</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>745497</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>1064595</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>497672</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>464910</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>807724</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>745001</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>163323</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>69651</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>938360</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>701327</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>390292</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>519892</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>176996</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>173917</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>268449</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>361760</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>377434</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>559314</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>1180767</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>382933</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>868741</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>411570</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>359567</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>935846</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>599411</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>209594</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>1133734</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>459825</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>615630</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>767203</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>30174</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>880126</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>736131</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>639018</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>1121378</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>856446</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>554614</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>1061365</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>892987</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>974123</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>703513</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>1007330</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>830545</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>118452</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>53358</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>948912</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>853832</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>599244</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>466782</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>1018114</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>539160</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>468419</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>229533</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>978444</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>886635</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>14022</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>617427</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>293227</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>589525</v>
+      </c>
+      <c r="II2" t="n">
+        <v>185935</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>34971</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>371543</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>1138345</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>470924</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>79955</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>779286</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>386539</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>914204</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>314191</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>655913</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>452259</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>368249</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>1106437</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>673822</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>22479</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>52990</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>958340</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>522065</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>994988</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>723781</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>659146</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>656927</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>846205</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>390413</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>813842</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>694008</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>94970</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>180376</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>93255</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>283585</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>681364</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>254281</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>685216</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>992803</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>251198</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>863175</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>1214491</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>796374</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>686845</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>341576</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>690951</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>604359</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>1160118</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>774657</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>1084148</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>68543</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>734828</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>561950</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>1191500</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>232821</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>648885</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>623124</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>474087</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>964187</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>1099442</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>300703</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>345118</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>559384</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>595600</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>8743</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>262647</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>124430</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>327999</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>47852</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>935518</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>1108217</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>570350</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>114331</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>340762</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>210077</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>411575</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>801009</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>142824</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>640720</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>1034119</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>762472</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>805145</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>451328</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>343544</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>156219</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>314917</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>459958</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>71813</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>332340</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>1001576</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>1171715</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>986988</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>709195</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>975859</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>768992</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>741453</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>122835</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>85071</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>56145</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>416150</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>972979</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>91474</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>187594</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>685894</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>581329</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>391272</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>801813</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>101025</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>50409</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>405897</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>382379</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>25273</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>9008</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>952937</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>302023</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>749850</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>845031</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>20477</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>505067</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>1012508</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>1074077</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>797872</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>454703</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>1156032</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>875864</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>606459</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>439675</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>253699</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>148136</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>759831</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>205</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>950901</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>227788</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>731327</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>819994</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>203644</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>524967</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>922716</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>579314</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>329802</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>997428</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>83064</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>415263</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>437155</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>1140600</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>956165</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>379815</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>721867</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>19224</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>34526</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>404928</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>463725</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>447759</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>11678</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>743230</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>835993</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>73816</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>663079</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>788733</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>1078271</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>567363</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>261677</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>158740</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>1047549</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>997830</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>419822</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>132083</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>839790</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>1206008</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>727031</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>442932</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>732029</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>1190216</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>791278</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>558664</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>215642</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>610388</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>1013137</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>63314</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>295742</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>5818</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>292078</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>302100</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>599380</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>320422</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>931969</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>1174827</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>448501</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>595996</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>283167</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>237323</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>21122</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>472343</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>117742</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>50472</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>169789</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>377351</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>246567</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>749427</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>809796</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>64302</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>24666</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>266425</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>223148</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>1104150</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>902055</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>350334</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>242812</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>231289</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>39746</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>1070196</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>1124077</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>39149</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>864807</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>439768</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>1010652</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>153938</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>1154907</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>287215</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>303123</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>1035346</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>833609</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>1169494</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>1208029</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>1220075</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>1097315</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>703007</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>98107</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>206918</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>1141644</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>1009205</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>248161</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>495423</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>485098</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>387323</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>1205669</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>315776</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>66270</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>416539</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>244617</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>690032</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>1017446</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>434752</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>38126</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>968992</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>1095708</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>1071425</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1196048</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>1107576</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>286548</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>124066</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>615479</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>848960</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>72456</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>673221</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>950491</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>826425</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>536363</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>655722</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>619709</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>414612</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>483354</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>883939</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>910589</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>84996</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>361399</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>531893</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1135276</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>746341</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>55824</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>297523</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>272318</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>1086311</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>505430</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>374810</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>1111850</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>398248</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>1038230</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>476887</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>709378</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>188459</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>129491</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>588296</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>465870</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>641973</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>594591</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>800036</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>571454</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>609598</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>545417</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>1025602</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>225482</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>500992</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>99760</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>311065</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>643392</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>227572</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>127948</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>1068199</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>272126</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>822886</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>993519</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>1042918</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>136098</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>112731</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>31364</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>254611</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>246589</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>439921</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>394344</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>1041580</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>870564</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>45418</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>897546</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>1003551</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>1221002</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>953379</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>941377</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>1133049</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>16795</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>389191</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>1046212</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>994978</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>519687</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>538342</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>739968</v>
+      </c>
+      <c r="US2" t="n">
+        <v>838920</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>626776</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>676331</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>968811</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>177328</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>524972</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>113135</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>947392</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>628864</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>677869</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>1002667</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>959706</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>918436</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>509563</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>946017</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>170834</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>240523</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>981052</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>859231</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>284665</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>593735</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>718322</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>486220</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>740182</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>164173</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>1165404</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>17866</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>1040907</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>1060518</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>456997</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>498512</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>874874</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>533752</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>823398</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>701162</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>424492</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>42046</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>998832</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>1022027</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>190144</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>1160087</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>429092</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>786553</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>777021</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>782388</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>402516</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>311354</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>276853</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>513885</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>555127</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>240455</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>159591</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>727696</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>343853</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>1066288</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>105457</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>109538</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>712869</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>50786</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>879012</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>649559</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>3244</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>103062</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>1187058</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>320232</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>309364</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>841418</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>105702</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>30908</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>653776</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>213045</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>1081864</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>551801</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>212482</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>160890</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>695646</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>629837</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>76878</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>1178273</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>1087584</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>182265</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>270991</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>576669</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>902133</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>632540</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>110571</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>1164847</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>574482</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>668113</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>872322</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>28377</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>199320</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>90309</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>426338</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>1029964</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>635129</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1125522</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>1057237</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>278257</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>735150</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>647185</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>301401</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>1091566</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>424822</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>892340</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>908890</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>385324</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>788294</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>1038168</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>225822</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>338882</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>1114607</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>610444</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>612128</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>1129761</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>233260</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>691264</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>471110</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>1156015</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>316252</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>1081715</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>366924</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>765871</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>379771</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>116895</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>889544</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>919139</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>266448</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>156966</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>1215729</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>712932</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>977225</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>117204</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>151723</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>926042</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>431377</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>576814</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>346554</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>673009</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>498761</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>115737</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>883389</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>911998</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>463182</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>907014</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>1015219</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>520831</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>21340</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>166057</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>1077511</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>430030</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>757651</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>646574</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>85533</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>515185</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>325207</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>1155616</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>191914</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>196610</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>1064521</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>203289</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>30794</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>144997</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>306213</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>611874</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>516465</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>102815</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>972536</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>827013</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>196971</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>345752</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>244021</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>43942</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>860667</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>293035</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>882334</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>989331</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>377505</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>816459</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>913976</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>1116407</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>509443</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>405330</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>61914</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>8026</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>984055</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>980038</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>1144185</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>274272</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>320524</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>138391</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>564098</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>1215202</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>448840</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>254677</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>851060</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>273062</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>1095643</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>1024707</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>1059899</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>217915</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>216914</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>544778</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>153540</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>55705</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>680236</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>127009</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>279497</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>697691</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1159785</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>171812</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>288029</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>371107</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>223441</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>531465</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>420175</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>486981</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>606497</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>99063</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>1043172</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>802702</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>311367</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>103701</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>224042</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>392951</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>752957</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>878159</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>147424</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>691490</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>1187011</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>1072140</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>168743</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>1182542</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>769039</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>1196682</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>886816</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>688258</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>1118657</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>859730</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>326811</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>811224</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>1101980</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>357382</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>1074844</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>526801</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>408640</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>731122</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>747557</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>502601</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>814149</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>295191</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>754640</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>1212144</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>305517</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>792670</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>525634</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>409873</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>366982</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>960040</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>715126</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>78282</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>487608</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>383831</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>208026</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>281110</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>58532</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>1140585</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>764610</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>1172491</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>939451</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>133209</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>367055</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>794668</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>970857</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>683183</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>829809</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>830672</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>375490</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>47599</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>956040</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>446949</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>320378</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>707379</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>1122743</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>846972</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>330308</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>876469</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>866978</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>783717</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>492570</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>424985</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>551149</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>12558</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>1093148</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>108814</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>256075</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>810756</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>195318</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>278297</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>138896</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>761609</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>967132</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>1152313</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>262026</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>121667</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>923459</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>399055</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>315507</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>331005</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>229300</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>334528</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>372528</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>590624</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>816499</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>364513</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>806219</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>45844</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>1199486</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>520224</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>141720</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>215042</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>661179</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>919945</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>636271</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>1046205</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>843174</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>35988</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>476962</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>983480</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>950556</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>779880</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>491525</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>200597</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>924397</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>356598</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>616011</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>603925</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>493774</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>775399</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>95388</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>94656</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>623971</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>58633</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>248957</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>28573</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>664594</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>898851</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>652298</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>1135826</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>1164296</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>1186917</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>434214</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>543254</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>783023</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>757764</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>541830</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>59898</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>1119741</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>508001</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>721341</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>260410</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>571680</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>347043</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>1126851</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>548095</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>294225</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>585986</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>806802</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>869485</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>834171</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1142503</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>909220</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>326934</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>36326</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1037700</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>807166</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>853557</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>874139</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>824513</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>351315</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>606270</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>698201</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>77579</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>771823</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>682743</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>785871</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>25119</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>900773</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>820559</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>1130125</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>528862</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>218362</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1109278</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>669970</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>238366</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>539199</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>1056557</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>324272</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>397758</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>1193249</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>841713</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>503114</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>403135</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>549930</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>708312</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>927586</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>134343</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>773807</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>988995</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>441395</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>196488</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>945778</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>1146230</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>528654</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>406725</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>34509</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>933409</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>4241</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>108558</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>585036</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>651036</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>837822</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>929421</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>222325</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>491337</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>895645</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>268666</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>89938</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>1176658</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>598134</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>1001359</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>140058</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>79789</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>236692</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>967939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>578687874</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4578098</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -1222,307 +4572,3907 @@
       <c r="CT1" t="inlineStr"/>
       <c r="CU1" t="inlineStr"/>
       <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>180719</v>
+        <v>498372</v>
       </c>
       <c r="B2" t="n">
-        <v>534880</v>
+        <v>836528</v>
       </c>
       <c r="C2" t="n">
-        <v>367133</v>
+        <v>716438</v>
       </c>
       <c r="D2" t="n">
-        <v>34011</v>
+        <v>1087173</v>
       </c>
       <c r="E2" t="n">
-        <v>522806</v>
+        <v>1040861</v>
       </c>
       <c r="F2" t="n">
-        <v>720745</v>
+        <v>1036099</v>
       </c>
       <c r="G2" t="n">
-        <v>632932</v>
+        <v>596297</v>
       </c>
       <c r="H2" t="n">
-        <v>581</v>
+        <v>609140</v>
       </c>
       <c r="I2" t="n">
-        <v>820049</v>
+        <v>946769</v>
       </c>
       <c r="J2" t="n">
-        <v>151442</v>
+        <v>332075</v>
       </c>
       <c r="K2" t="n">
-        <v>857513</v>
+        <v>963495</v>
       </c>
       <c r="L2" t="n">
-        <v>494870</v>
+        <v>432483</v>
       </c>
       <c r="M2" t="n">
-        <v>171360</v>
+        <v>120011</v>
       </c>
       <c r="N2" t="n">
-        <v>675125</v>
+        <v>788810</v>
       </c>
       <c r="O2" t="n">
-        <v>430788</v>
+        <v>994092</v>
       </c>
       <c r="P2" t="n">
-        <v>575023</v>
+        <v>680058</v>
       </c>
       <c r="Q2" t="n">
-        <v>673979</v>
+        <v>1200018</v>
       </c>
       <c r="R2" t="n">
-        <v>250003</v>
+        <v>217412</v>
       </c>
       <c r="S2" t="n">
-        <v>107630</v>
+        <v>87865</v>
       </c>
       <c r="T2" t="n">
-        <v>340502</v>
+        <v>1052827</v>
       </c>
       <c r="U2" t="n">
-        <v>184189</v>
+        <v>684313</v>
       </c>
       <c r="V2" t="n">
-        <v>160895</v>
+        <v>163410</v>
       </c>
       <c r="W2" t="n">
-        <v>578200</v>
+        <v>1025772</v>
       </c>
       <c r="X2" t="n">
-        <v>470836</v>
+        <v>303216</v>
       </c>
       <c r="Y2" t="n">
-        <v>790288</v>
+        <v>698841</v>
       </c>
       <c r="Z2" t="n">
-        <v>459086</v>
+        <v>854288</v>
       </c>
       <c r="AA2" t="n">
-        <v>610581</v>
+        <v>1131327</v>
       </c>
       <c r="AB2" t="n">
-        <v>582102</v>
+        <v>967946</v>
       </c>
       <c r="AC2" t="n">
-        <v>292219</v>
+        <v>326854</v>
       </c>
       <c r="AD2" t="n">
-        <v>476491</v>
+        <v>365435</v>
       </c>
       <c r="AE2" t="n">
-        <v>214355</v>
+        <v>192555</v>
       </c>
       <c r="AF2" t="n">
-        <v>264773</v>
+        <v>378916</v>
       </c>
       <c r="AG2" t="n">
-        <v>693821</v>
+        <v>427130</v>
       </c>
       <c r="AH2" t="n">
-        <v>193110</v>
+        <v>204412</v>
       </c>
       <c r="AI2" t="n">
-        <v>638589</v>
+        <v>354471</v>
       </c>
       <c r="AJ2" t="n">
-        <v>122105</v>
+        <v>746969</v>
       </c>
       <c r="AK2" t="n">
-        <v>102070</v>
+        <v>209730</v>
       </c>
       <c r="AL2" t="n">
-        <v>26807</v>
+        <v>238250</v>
       </c>
       <c r="AM2" t="n">
-        <v>709112</v>
+        <v>83267</v>
       </c>
       <c r="AN2" t="n">
-        <v>645876</v>
+        <v>847700</v>
       </c>
       <c r="AO2" t="n">
-        <v>750902</v>
+        <v>982825</v>
       </c>
       <c r="AP2" t="n">
-        <v>100614</v>
+        <v>88440</v>
       </c>
       <c r="AQ2" t="n">
-        <v>59686</v>
+        <v>46988</v>
       </c>
       <c r="AR2" t="n">
-        <v>208780</v>
+        <v>245267</v>
       </c>
       <c r="AS2" t="n">
-        <v>634984</v>
+        <v>563935</v>
       </c>
       <c r="AT2" t="n">
-        <v>310753</v>
+        <v>1149003</v>
       </c>
       <c r="AU2" t="n">
-        <v>257698</v>
+        <v>238282</v>
       </c>
       <c r="AV2" t="n">
-        <v>338947</v>
+        <v>516731</v>
       </c>
       <c r="AW2" t="n">
-        <v>258054</v>
+        <v>216983</v>
       </c>
       <c r="AX2" t="n">
-        <v>72671</v>
+        <v>828076</v>
       </c>
       <c r="AY2" t="n">
-        <v>657927</v>
+        <v>232926</v>
       </c>
       <c r="AZ2" t="n">
-        <v>515019</v>
+        <v>27923</v>
       </c>
       <c r="BA2" t="n">
-        <v>609467</v>
+        <v>1049245</v>
       </c>
       <c r="BB2" t="n">
-        <v>357207</v>
+        <v>472512</v>
       </c>
       <c r="BC2" t="n">
-        <v>139455</v>
+        <v>911312</v>
       </c>
       <c r="BD2" t="n">
-        <v>730695</v>
+        <v>328850</v>
       </c>
       <c r="BE2" t="n">
-        <v>756207</v>
+        <v>296823</v>
       </c>
       <c r="BF2" t="n">
-        <v>768301</v>
+        <v>224660</v>
       </c>
       <c r="BG2" t="n">
-        <v>295409</v>
+        <v>420101</v>
       </c>
       <c r="BH2" t="n">
-        <v>83100</v>
+        <v>228002</v>
       </c>
       <c r="BI2" t="n">
-        <v>289687</v>
+        <v>790935</v>
       </c>
       <c r="BJ2" t="n">
-        <v>516112</v>
+        <v>614137</v>
       </c>
       <c r="BK2" t="n">
-        <v>50548</v>
+        <v>512025</v>
       </c>
       <c r="BL2" t="n">
-        <v>792461</v>
+        <v>741113</v>
       </c>
       <c r="BM2" t="n">
-        <v>809328</v>
+        <v>1119064</v>
       </c>
       <c r="BN2" t="n">
-        <v>61934</v>
+        <v>676914</v>
       </c>
       <c r="BO2" t="n">
-        <v>571019</v>
+        <v>287250</v>
       </c>
       <c r="BP2" t="n">
-        <v>732359</v>
+        <v>737160</v>
       </c>
       <c r="BQ2" t="n">
-        <v>836240</v>
+        <v>1004475</v>
       </c>
       <c r="BR2" t="n">
-        <v>516234</v>
+        <v>388518</v>
       </c>
       <c r="BS2" t="n">
-        <v>325609</v>
+        <v>1120220</v>
       </c>
       <c r="BT2" t="n">
-        <v>443452</v>
+        <v>676140</v>
       </c>
       <c r="BU2" t="n">
-        <v>822975</v>
+        <v>1177870</v>
       </c>
       <c r="BV2" t="n">
-        <v>391378</v>
+        <v>1008819</v>
       </c>
       <c r="BW2" t="n">
-        <v>738149</v>
+        <v>967661</v>
       </c>
       <c r="BX2" t="n">
-        <v>87597</v>
+        <v>584967</v>
       </c>
       <c r="BY2" t="n">
-        <v>430466</v>
+        <v>946283</v>
       </c>
       <c r="BZ2" t="n">
-        <v>20074</v>
+        <v>299426</v>
       </c>
       <c r="CA2" t="n">
-        <v>223266</v>
+        <v>76213</v>
       </c>
       <c r="CB2" t="n">
-        <v>371192</v>
+        <v>342227</v>
       </c>
       <c r="CC2" t="n">
-        <v>113494</v>
+        <v>692494</v>
       </c>
       <c r="CD2" t="n">
-        <v>220830</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>548820</v>
+        <v>564094</v>
       </c>
       <c r="CF2" t="n">
-        <v>490249</v>
+        <v>751517</v>
       </c>
       <c r="CG2" t="n">
-        <v>773142</v>
+        <v>492369</v>
       </c>
       <c r="CH2" t="n">
-        <v>232694</v>
+        <v>1071954</v>
       </c>
       <c r="CI2" t="n">
-        <v>707</v>
+        <v>122549</v>
       </c>
       <c r="CJ2" t="n">
-        <v>465142</v>
+        <v>90563</v>
       </c>
       <c r="CK2" t="n">
-        <v>232947</v>
+        <v>612853</v>
       </c>
       <c r="CL2" t="n">
-        <v>407792</v>
+        <v>260198</v>
       </c>
       <c r="CM2" t="n">
-        <v>291168</v>
+        <v>182933</v>
       </c>
       <c r="CN2" t="n">
+        <v>1188845</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>523190</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1058209</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>227701</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>113595</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>834853</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>1128353</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>206085</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>258462</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>210497</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>411764</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>753666</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>681533</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>466950</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>567450</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>574038</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>589926</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>820365</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>858638</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>246148</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>623293</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>113154</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>534743</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>738732</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>231160</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1203709</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1165311</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1082377</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>274939</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>927033</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>140366</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>532896</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>880342</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>241068</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>223719</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>384168</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1203087</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>479803</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>612540</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>49878</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>726859</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>892013</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1134054</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1029147</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>71867</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>920883</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>137501</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>328771</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>56683</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>5461</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1142677</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>254198</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1171577</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>342223</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>466352</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>554320</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>36773</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>833623</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>779525</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>309726</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>898872</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1014393</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>874005</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>454056</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>376473</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1124373</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>869710</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>696837</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>265185</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>802155</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>588841</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>169282</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1139187</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>1083692</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>693026</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1019248</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>19204</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>609412</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>282023</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>659826</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>529479</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>1010808</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>461486</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>781801</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>801837</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>1013664</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>767274</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>443426</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>969473</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>723428</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>768911</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>441420</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>605187</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>714255</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>99873</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>883475</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>251804</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>220845</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>601199</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>318223</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>947378</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>852072</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>21794</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>547316</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>444531</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>1057526</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>122053</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>522355</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>207883</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>630179</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>394555</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>839446</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>387972</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>923102</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>960686</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>233858</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>657314</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>371798</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>145829</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>462765</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>809513</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>1093245</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>68055</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>596837</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>475060</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>206041</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>1054289</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>584167</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>1151279</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>1147929</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>4321</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>241561</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>1030658</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>847814</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>399788</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>1009108</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>840319</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>358173</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>772297</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>427129</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>950658</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>109192</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>712624</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>466123</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>939647</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>199380</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>402798</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>127721</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>485460</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>157507</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>509713</v>
+      </c>
+      <c r="II2" t="n">
+        <v>799688</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>41559</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>812943</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>712126</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>368184</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>82025</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>268522</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>452735</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>607521</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>305754</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>526455</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>366212</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>1060861</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>1064248</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>418296</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>279303</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>857242</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>18181</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>132598</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>774926</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>940555</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>203228</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>504985</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>84901</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>1013832</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>295271</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>92106</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>837646</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1120035</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>977372</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>1044219</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>300583</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>447078</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>1114248</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>906694</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>264401</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>175941</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>764981</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>370094</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>1032603</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>512639</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>187448</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1091376</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>396530</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>968963</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>237183</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>935647</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>620980</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>952459</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>254329</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>1157400</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>181815</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>986289</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>505246</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>737248</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>380494</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>688876</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>107059</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>540079</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>766616</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>423804</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>384945</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>642734</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>785813</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>1090806</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>62731</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>1181929</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>940732</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>591456</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>135345</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>33960</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>117295</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>62361</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>200911</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>1213288</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>1190745</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>661399</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>10994</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>489950</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>799106</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>1159155</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>158183</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>884587</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>609662</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>815603</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>664117</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>345634</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>13668</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>88867</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>1186277</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>930714</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>548562</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>721502</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>862715</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>908415</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>1010638</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>717376</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>156451</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>44666</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>708479</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>165843</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>908270</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>518634</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>94977</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>367192</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>188554</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>97064</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>53387</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>1065847</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>806833</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>275406</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>51801</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>439815</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>991850</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>304382</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>120135</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>654482</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>579453</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>356535</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>414007</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>26818</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>531628</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>1181169</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>458442</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>176259</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>175612</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>541585</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>38928</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>114738</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>505917</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>707234</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>100903</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>924225</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>1078355</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>592985</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>482509</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>64829</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>863310</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>679003</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>174796</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>1175818</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>184382</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>132660</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>903825</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>242070</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>887720</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>1069635</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>320866</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>958433</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>771288</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>362383</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>14344</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>159804</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>724808</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>1170549</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>16725</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>301681</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>878476</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>526202</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>1145346</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>449240</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>179760</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>870017</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>383849</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>618450</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>125706</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>214963</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>544909</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>415531</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>57295</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>792936</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>403097</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>1023373</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>463208</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>401092</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>26633</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>604094</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>925076</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>59030</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>677333</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>728300</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>188889</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>691250</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>114515</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>331541</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>69841</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>212543</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>1137836</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>499367</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>818802</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>722320</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>963361</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>356784</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>86412</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>153669</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>952163</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>1052265</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>957243</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>39681</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>716957</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>814098</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>156457</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>980750</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1083754</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>569616</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>751389</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>1205336</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>707818</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>826148</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>945980</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>795586</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>649778</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>542877</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>551379</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>870048</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>435569</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>686570</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>1109584</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>744232</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>1005475</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>362202</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>269818</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>896828</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>1027833</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>217026</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>432730</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>305921</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>566954</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>657202</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>883161</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>783492</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>395462</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>1055218</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>1113715</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>686969</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>1099049</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>62597</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>124359</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>977480</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>630042</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>937300</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>878494</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>590133</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>1032593</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>151865</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>933287</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>574387</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>629962</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>501221</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>831321</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>577981</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>645205</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>12630</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>7250</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>867218</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>198271</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>1166806</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>638371</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>998698</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>340910</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>141766</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>872531</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1106001</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>269187</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>899201</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>538000</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>573661</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>245966</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>261836</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>841864</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>996657</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>481533</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>1037247</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>468879</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>229969</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>137112</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>1038191</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>1135551</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>742394</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>1153220</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>915675</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>851271</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>475874</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>925645</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>500787</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>1100158</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>345072</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>1051528</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>903892</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>524332</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>168305</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>139389</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>1174344</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>688805</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>6128</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>333785</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>44509</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>711520</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>824112</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>831878</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>1210206</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>487662</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>596117</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>961846</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>30139</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>671938</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>256456</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>849642</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>292243</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>652118</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>695035</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>449616</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>169771</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>887283</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>583838</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>622611</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>6829</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>914199</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>334359</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>666601</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>39122</v>
+      </c>
+      <c r="US2" t="n">
+        <v>57937</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>1020616</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>83005</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>763298</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>664559</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>21981</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>129780</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>255401</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>78798</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>903816</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>960892</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>1045604</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>454190</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>1194335</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>461408</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>415035</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>392349</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>1000919</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>734427</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>955134</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>987054</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>652963</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>358273</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>363366</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>49131</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>431442</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>418223</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>750656</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>935826</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>733356</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>1185308</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>546774</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>147023</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>97842</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>789380</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>166119</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>1124356</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>407525</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>1096627</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>295210</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>624929</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>353207</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>22333</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>196736</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>1161061</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>488945</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>61474</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>1046675</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>877364</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>895140</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>973432</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>535009</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>431143</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>34456</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>843331</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>247970</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>28595</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>260458</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>587760</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>742916</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>283682</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>1006004</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>426378</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>560528</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>804431</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>778060</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>192250</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>234508</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>418562</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>916582</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>324519</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>701557</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>47656</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>278555</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>728806</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>300107</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>628289</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>601505</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>529947</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>438406</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>491466</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>1162373</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>949520</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>919342</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>349333</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>72933</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>411150</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>43437</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>881108</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>1196686</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>68970</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>757392</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>94453</v>
+      </c>
+      <c r="YH2" t="n">
         <v>0</v>
       </c>
-      <c r="CO2" t="n">
-        <v>642928</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>379855</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>130694</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>134663</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>70827</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>412660</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>182669</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>322501</v>
+      <c r="YI2" t="n">
+        <v>148594</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>96280</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>641476</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>972227</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>913459</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>288166</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>635556</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>659747</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>171909</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>336699</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>161605</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1088188</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>636717</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>1072463</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>346022</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>148988</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>981776</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>12851</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>859029</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>33982</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>584115</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>599979</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>617419</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>1015446</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>453753</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>1109847</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>498026</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>706004</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>632668</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>495829</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>406694</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>1027300</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>71995</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>316234</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>733361</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>874824</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>894208</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>1107943</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>919034</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>536287</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>811196</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>184237</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>234940</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>472206</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>1060776</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>555645</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>90474</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>24149</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>325818</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>815769</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>1046685</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>66764</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>931485</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>9883</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1078167</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>659887</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>191130</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>1001472</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>5217</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>404417</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>211523</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>105860</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>672951</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>316241</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>679868</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>1018250</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>474433</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>1095481</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>754050</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1124415</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>781640</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>808310</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>559714</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>353470</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>266010</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>761758</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>109566</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>74892</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>142125</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>382382</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>551884</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>134425</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>796299</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>322972</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>319395</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>906334</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>211076</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>844280</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>517981</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>325335</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>978721</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>704752</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>777213</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>509839</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>644995</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>544405</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>313853</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>760757</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>668347</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>557612</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>593561</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>154263</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>787085</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>806232</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>248753</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>717106</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>17739</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>389331</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>746431</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>792868</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>331638</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>339392</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>43318</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>204759</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>502582</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>1117557</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>130269</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>117907</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>1129956</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>1165618</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>77286</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>863656</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>618236</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>636954</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>851306</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>1104294</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>508162</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>146008</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>472300</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>1113779</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>436352</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>641128</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>777265</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>634805</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>222769</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>377633</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>944218</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>1076879</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>459919</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>191108</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>723372</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>694737</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>424326</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>889402</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>1132466</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>786553</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>399351</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>390660</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>437770</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>865930</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>1102997</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>682428</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>272992</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>639948</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>280002</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>249742</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>1199966</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>1199438</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>422526</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>31448</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>168014</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>336450</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>746331</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>478773</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>75856</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>755869</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>439942</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>393876</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>322477</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>859610</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>727932</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>221641</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>129923</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>823560</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>287774</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>602481</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>595679</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>740101</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>1186641</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>773015</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>939047</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>891548</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>826443</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>653050</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>1158022</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>124839</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>900319</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>793487</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>282605</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>1154248</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>1144077</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>379628</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>408974</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>185517</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>667516</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>558685</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>804802</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>341087</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>374434</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>119005</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>291893</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>930257</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>702001</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>162602</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>700637</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>573041</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>894415</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>2179</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>447242</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>579528</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>1105595</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>274277</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1066987</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>78237</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>284481</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>373930</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>830726</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>817133</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>1010546</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>195581</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>529704</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>552117</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>421284</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>344</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>989741</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>228704</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>253207</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>608868</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>1041112</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>782975</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>1072845</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>386528</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>101794</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>307316</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>1078074</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>290008</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>1211535</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>110872</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>178085</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>312995</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>361269</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>1208465</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>973796</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>150517</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>513954</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>218553</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>770568</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>539394</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>507855</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>763364</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>647930</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>983854</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1000782</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>195590</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>886055</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>821285</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>515571</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>570087</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>106071</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>667369</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>873317</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>851655</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>812252</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>263344</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>103265</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>483879</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>348788</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1129546</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>52218</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>620187</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>30782</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>143394</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>468498</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>37517</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>80290</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>102505</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>824154</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>220831</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>517689</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>647581</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>289078</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>1073144</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>313264</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>758483</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>1136458</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>992856</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>510839</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>338891</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>271672</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>623378</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>480218</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>476583</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>350035</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>200289</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>390587</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>1150725</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>956053</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>383796</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>171255</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>270637</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>373766</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>1100429</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>971172</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>672093</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>993047</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>521326</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>456924</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>1020965</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>921113</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>1173088</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>246723</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>310789</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>836880</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>408363</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>485596</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>569006</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>685755</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>444267</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>1035139</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>17563</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>987604</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>731294</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1181011</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>273501</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>1193692</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>298876</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>563355</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>774657</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>421888</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>492548</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>397101</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>1155109</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>251420</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>57615</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>699421</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>540923</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>430215</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>1061149</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>578257</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>495898</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>616526</v>
       </c>
     </row>
   </sheetData>
@@ -1544,7 +8494,7 @@
         <v>321</v>
       </c>
       <c r="B1" t="n">
-        <v>1286</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2">
@@ -1583,42 +8533,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9808</v>
+        <v>9814</v>
       </c>
       <c r="B1" t="n">
-        <v>19826</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>46</v>
+        <v>486</v>
       </c>
       <c r="B2" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C2" t="n">
-        <v>1135</v>
+        <v>925</v>
       </c>
       <c r="D2" t="n">
-        <v>979</v>
+        <v>725</v>
       </c>
       <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>366</v>
+      </c>
+      <c r="G2" t="n">
+        <v>209</v>
+      </c>
+      <c r="H2" t="n">
+        <v>562</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1170</v>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>755</v>
-      </c>
-      <c r="G2" t="n">
-        <v>552</v>
-      </c>
-      <c r="H2" t="n">
-        <v>604</v>
-      </c>
-      <c r="I2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J2" t="n">
-        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -1637,10 +8587,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>10212</v>
+        <v>10203</v>
       </c>
       <c r="B1" t="n">
-        <v>10108</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="2">
@@ -1651,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1136</v>
+        <v>1247</v>
       </c>
       <c r="D2" t="n">
-        <v>669</v>
+        <v>833</v>
       </c>
       <c r="E2" t="n">
-        <v>616</v>
+        <v>650</v>
       </c>
       <c r="F2" t="n">
         <v>179</v>
@@ -1669,10 +8619,10 @@
         <v>375</v>
       </c>
       <c r="I2" t="n">
-        <v>769</v>
+        <v>917</v>
       </c>
       <c r="J2" t="n">
-        <v>1051</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -1691,72 +8641,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>17100</v>
+        <v>16890</v>
       </c>
       <c r="B1" t="n">
-        <v>330064</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>514</v>
+        <v>167</v>
       </c>
       <c r="B2" t="n">
-        <v>1237</v>
+        <v>408</v>
       </c>
       <c r="C2" t="n">
-        <v>1078</v>
+        <v>900</v>
       </c>
       <c r="D2" t="n">
-        <v>752</v>
+        <v>1048</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>457</v>
       </c>
       <c r="G2" t="n">
-        <v>392</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
-        <v>466</v>
+        <v>119</v>
       </c>
       <c r="I2" t="n">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="J2" t="n">
-        <v>913</v>
+        <v>630</v>
       </c>
       <c r="K2" t="n">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="L2" t="n">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="M2" t="n">
-        <v>740</v>
+        <v>556</v>
       </c>
       <c r="N2" t="n">
-        <v>1329</v>
+        <v>935</v>
       </c>
       <c r="O2" t="n">
-        <v>640</v>
+        <v>1445</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>886</v>
       </c>
       <c r="Q2" t="n">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="R2" t="n">
-        <v>912</v>
+        <v>1200</v>
       </c>
       <c r="S2" t="n">
-        <v>556</v>
+        <v>757</v>
       </c>
       <c r="T2" t="n">
-        <v>370</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1775,72 +8725,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>17260</v>
+        <v>17644</v>
       </c>
       <c r="B1" t="n">
-        <v>336185</v>
+        <v>9596</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="B2" t="n">
-        <v>598</v>
+        <v>1256</v>
       </c>
       <c r="C2" t="n">
-        <v>816</v>
+        <v>567</v>
       </c>
       <c r="D2" t="n">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>635</v>
+        <v>1137</v>
       </c>
       <c r="G2" t="n">
-        <v>449</v>
+        <v>789</v>
       </c>
       <c r="H2" t="n">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="I2" t="n">
-        <v>709</v>
+        <v>1137</v>
       </c>
       <c r="J2" t="n">
-        <v>1495</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>682</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="M2" t="n">
-        <v>280</v>
+        <v>194</v>
       </c>
       <c r="N2" t="n">
-        <v>1249</v>
+        <v>1489</v>
       </c>
       <c r="O2" t="n">
-        <v>1049</v>
+        <v>923</v>
       </c>
       <c r="P2" t="n">
-        <v>1204</v>
+        <v>377</v>
       </c>
       <c r="Q2" t="n">
-        <v>556</v>
+        <v>475</v>
       </c>
       <c r="R2" t="n">
-        <v>1120</v>
+        <v>993</v>
       </c>
       <c r="S2" t="n">
-        <v>986</v>
+        <v>859</v>
       </c>
       <c r="T2" t="n">
-        <v>267</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>
@@ -1862,7 +8812,7 @@
         <v>94122</v>
       </c>
       <c r="B1" t="n">
-        <v>29152</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="2">
@@ -1913,42 +8863,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>98721</v>
+        <v>98363</v>
       </c>
       <c r="B1" t="n">
-        <v>26720</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>801</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1033</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>6539</v>
+        <v>4829</v>
       </c>
       <c r="D2" t="n">
-        <v>8547</v>
+        <v>6855</v>
       </c>
       <c r="E2" t="n">
-        <v>6914</v>
+        <v>5204</v>
       </c>
       <c r="F2" t="n">
-        <v>9691</v>
+        <v>7981</v>
       </c>
       <c r="G2" t="n">
-        <v>4850</v>
+        <v>3140</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2070</v>
+        <v>13652</v>
       </c>
       <c r="J2" t="n">
-        <v>5521</v>
+        <v>3829</v>
       </c>
     </row>
   </sheetData>
@@ -1967,312 +8917,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6537532</v>
+        <v>6415915</v>
       </c>
       <c r="B1" t="n">
-        <v>3600009</v>
+        <v>3611378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32329</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>99535</v>
+        <v>117730</v>
       </c>
       <c r="C2" t="n">
-        <v>99360</v>
+        <v>70278</v>
       </c>
       <c r="D2" t="n">
-        <v>22866</v>
+        <v>96401</v>
       </c>
       <c r="E2" t="n">
-        <v>2229</v>
+        <v>93292</v>
       </c>
       <c r="F2" t="n">
-        <v>73526</v>
+        <v>111950</v>
       </c>
       <c r="G2" t="n">
-        <v>44919</v>
+        <v>105122</v>
       </c>
       <c r="H2" t="n">
-        <v>104218</v>
+        <v>21615</v>
       </c>
       <c r="I2" t="n">
-        <v>26525</v>
+        <v>33703</v>
       </c>
       <c r="J2" t="n">
-        <v>40549</v>
+        <v>31990</v>
       </c>
       <c r="K2" t="n">
-        <v>113380</v>
+        <v>76684</v>
       </c>
       <c r="L2" t="n">
-        <v>2602</v>
+        <v>21752</v>
       </c>
       <c r="M2" t="n">
-        <v>131089</v>
+        <v>109077</v>
       </c>
       <c r="N2" t="n">
-        <v>122710</v>
+        <v>89517</v>
       </c>
       <c r="O2" t="n">
-        <v>191</v>
+        <v>112459</v>
       </c>
       <c r="P2" t="n">
-        <v>491</v>
+        <v>59067</v>
       </c>
       <c r="Q2" t="n">
-        <v>7989</v>
+        <v>55125</v>
       </c>
       <c r="R2" t="n">
-        <v>42364</v>
+        <v>5429</v>
       </c>
       <c r="S2" t="n">
-        <v>41344</v>
+        <v>107738</v>
       </c>
       <c r="T2" t="n">
-        <v>67192</v>
+        <v>17670</v>
       </c>
       <c r="U2" t="n">
-        <v>86249</v>
+        <v>115606</v>
       </c>
       <c r="V2" t="n">
-        <v>73276</v>
+        <v>124753</v>
       </c>
       <c r="W2" t="n">
-        <v>23875</v>
+        <v>27581</v>
       </c>
       <c r="X2" t="n">
-        <v>13907</v>
+        <v>96736</v>
       </c>
       <c r="Y2" t="n">
-        <v>5518</v>
+        <v>33062</v>
       </c>
       <c r="Z2" t="n">
-        <v>108930</v>
+        <v>19940</v>
       </c>
       <c r="AA2" t="n">
-        <v>79738</v>
+        <v>103122</v>
       </c>
       <c r="AB2" t="n">
-        <v>53155</v>
+        <v>91387</v>
       </c>
       <c r="AC2" t="n">
-        <v>20345</v>
+        <v>19301</v>
       </c>
       <c r="AD2" t="n">
-        <v>15545</v>
+        <v>43258</v>
       </c>
       <c r="AE2" t="n">
-        <v>6004</v>
+        <v>44363</v>
       </c>
       <c r="AF2" t="n">
-        <v>113340</v>
+        <v>66946</v>
       </c>
       <c r="AG2" t="n">
-        <v>78522</v>
+        <v>47614</v>
       </c>
       <c r="AH2" t="n">
-        <v>50096</v>
+        <v>106191</v>
       </c>
       <c r="AI2" t="n">
-        <v>45195</v>
+        <v>82604</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80908</v>
+        <v>6496</v>
       </c>
       <c r="AK2" t="n">
-        <v>21930</v>
+        <v>981</v>
       </c>
       <c r="AL2" t="n">
-        <v>71711</v>
+        <v>40531</v>
       </c>
       <c r="AM2" t="n">
-        <v>92944</v>
+        <v>128713</v>
       </c>
       <c r="AN2" t="n">
-        <v>9795</v>
+        <v>36040</v>
       </c>
       <c r="AO2" t="n">
-        <v>121845</v>
+        <v>119918</v>
       </c>
       <c r="AP2" t="n">
-        <v>18938</v>
+        <v>74809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>130916</v>
+        <v>64812</v>
       </c>
       <c r="AR2" t="n">
-        <v>68599</v>
+        <v>101512</v>
       </c>
       <c r="AS2" t="n">
-        <v>35227</v>
+        <v>59787</v>
       </c>
       <c r="AT2" t="n">
-        <v>60291</v>
+        <v>59949</v>
       </c>
       <c r="AU2" t="n">
-        <v>26525</v>
+        <v>57624</v>
       </c>
       <c r="AV2" t="n">
-        <v>120978</v>
+        <v>12675</v>
       </c>
       <c r="AW2" t="n">
-        <v>125444</v>
+        <v>48392</v>
       </c>
       <c r="AX2" t="n">
-        <v>62761</v>
+        <v>63608</v>
       </c>
       <c r="AY2" t="n">
-        <v>114280</v>
+        <v>47335</v>
       </c>
       <c r="AZ2" t="n">
-        <v>78638</v>
+        <v>11886</v>
       </c>
       <c r="BA2" t="n">
-        <v>93289</v>
+        <v>44014</v>
       </c>
       <c r="BB2" t="n">
-        <v>62213</v>
+        <v>71816</v>
       </c>
       <c r="BC2" t="n">
-        <v>94949</v>
+        <v>85389</v>
       </c>
       <c r="BD2" t="n">
-        <v>11495</v>
+        <v>79679</v>
       </c>
       <c r="BE2" t="n">
-        <v>4152</v>
+        <v>15853</v>
       </c>
       <c r="BF2" t="n">
-        <v>31183</v>
+        <v>95912</v>
       </c>
       <c r="BG2" t="n">
-        <v>8933</v>
+        <v>8576</v>
       </c>
       <c r="BH2" t="n">
-        <v>117349</v>
+        <v>1622</v>
       </c>
       <c r="BI2" t="n">
-        <v>74166</v>
+        <v>113801</v>
       </c>
       <c r="BJ2" t="n">
-        <v>89040</v>
+        <v>24665</v>
       </c>
       <c r="BK2" t="n">
-        <v>17396</v>
+        <v>402</v>
       </c>
       <c r="BL2" t="n">
-        <v>86532</v>
+        <v>50123</v>
       </c>
       <c r="BM2" t="n">
-        <v>16408</v>
+        <v>56564</v>
       </c>
       <c r="BN2" t="n">
-        <v>34435</v>
+        <v>62696</v>
       </c>
       <c r="BO2" t="n">
-        <v>88225</v>
+        <v>68099</v>
       </c>
       <c r="BP2" t="n">
-        <v>83743</v>
+        <v>14435</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7977</v>
+        <v>115252</v>
       </c>
       <c r="BR2" t="n">
-        <v>84498</v>
+        <v>80086</v>
       </c>
       <c r="BS2" t="n">
-        <v>90541</v>
+        <v>118856</v>
       </c>
       <c r="BT2" t="n">
-        <v>95785</v>
+        <v>123930</v>
       </c>
       <c r="BU2" t="n">
-        <v>38405</v>
+        <v>7860</v>
       </c>
       <c r="BV2" t="n">
-        <v>28047</v>
+        <v>35713</v>
       </c>
       <c r="BW2" t="n">
-        <v>111774</v>
+        <v>36574</v>
       </c>
       <c r="BX2" t="n">
-        <v>91976</v>
+        <v>3114</v>
       </c>
       <c r="BY2" t="n">
-        <v>58922</v>
+        <v>19730</v>
       </c>
       <c r="BZ2" t="n">
-        <v>103063</v>
+        <v>83425</v>
       </c>
       <c r="CA2" t="n">
-        <v>54577</v>
+        <v>39062</v>
       </c>
       <c r="CB2" t="n">
-        <v>118676</v>
+        <v>24719</v>
       </c>
       <c r="CC2" t="n">
-        <v>59661</v>
+        <v>39099</v>
       </c>
       <c r="CD2" t="n">
-        <v>108997</v>
+        <v>72459</v>
       </c>
       <c r="CE2" t="n">
-        <v>49244</v>
+        <v>76048</v>
       </c>
       <c r="CF2" t="n">
-        <v>18313</v>
+        <v>109613</v>
       </c>
       <c r="CG2" t="n">
-        <v>67872</v>
+        <v>50277</v>
       </c>
       <c r="CH2" t="n">
-        <v>0</v>
+        <v>29533</v>
       </c>
       <c r="CI2" t="n">
-        <v>64842</v>
+        <v>69436</v>
       </c>
       <c r="CJ2" t="n">
-        <v>31740</v>
+        <v>123983</v>
       </c>
       <c r="CK2" t="n">
-        <v>52461</v>
+        <v>79268</v>
       </c>
       <c r="CL2" t="n">
-        <v>106582</v>
+        <v>86417</v>
       </c>
       <c r="CM2" t="n">
-        <v>37510</v>
+        <v>16984</v>
       </c>
       <c r="CN2" t="n">
-        <v>50072</v>
+        <v>4689</v>
       </c>
       <c r="CO2" t="n">
-        <v>29139</v>
+        <v>89746</v>
       </c>
       <c r="CP2" t="n">
-        <v>11722</v>
+        <v>12769</v>
       </c>
       <c r="CQ2" t="n">
-        <v>57353</v>
+        <v>101205</v>
       </c>
       <c r="CR2" t="n">
-        <v>47570</v>
+        <v>52516</v>
       </c>
       <c r="CS2" t="n">
-        <v>42577</v>
+        <v>29274</v>
       </c>
       <c r="CT2" t="n">
-        <v>77516</v>
+        <v>10623</v>
       </c>
       <c r="CU2" t="n">
-        <v>103160</v>
+        <v>54248</v>
       </c>
       <c r="CV2" t="n">
-        <v>127793</v>
+        <v>26804</v>
       </c>
     </row>
   </sheetData>
